--- a/data/nzd0185/nzd0185.xlsx
+++ b/data/nzd0185/nzd0185.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I549"/>
+  <dimension ref="A1:I550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18542,15 +18542,48 @@
         <v>348.47</v>
       </c>
       <c r="F549" t="n">
-        <v>345.28</v>
+        <v>338.54</v>
       </c>
       <c r="G549" t="n">
-        <v>337.15</v>
+        <v>330.56</v>
       </c>
       <c r="H549" t="n">
         <v>318.71</v>
       </c>
       <c r="I549" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>353.93</v>
+      </c>
+      <c r="C550" t="n">
+        <v>352.06</v>
+      </c>
+      <c r="D550" t="n">
+        <v>347.29</v>
+      </c>
+      <c r="E550" t="n">
+        <v>348.12</v>
+      </c>
+      <c r="F550" t="n">
+        <v>337.92</v>
+      </c>
+      <c r="G550" t="n">
+        <v>329.67</v>
+      </c>
+      <c r="H550" t="n">
+        <v>316.96</v>
+      </c>
+      <c r="I550" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18567,7 +18600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B653"/>
+  <dimension ref="A1:B655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25100,6 +25133,26 @@
       </c>
       <c r="B653" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>-0.41</v>
       </c>
     </row>
   </sheetData>
@@ -25268,28 +25321,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2060116605542013</v>
+        <v>-0.2057847854639174</v>
       </c>
       <c r="J2" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K2" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05852936251742047</v>
+        <v>0.05863853860149359</v>
       </c>
       <c r="M2" t="n">
-        <v>4.826494100399379</v>
+        <v>4.818575694191575</v>
       </c>
       <c r="N2" t="n">
-        <v>35.94927203531844</v>
+        <v>35.88443599849348</v>
       </c>
       <c r="O2" t="n">
-        <v>5.995771179366208</v>
+        <v>5.990361925501119</v>
       </c>
       <c r="P2" t="n">
-        <v>358.7237693102089</v>
+        <v>358.7214176207977</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25346,28 +25399,28 @@
         <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1756147591984641</v>
+        <v>0.1757218128160311</v>
       </c>
       <c r="J3" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K3" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02925990771759424</v>
+        <v>0.02941417649984945</v>
       </c>
       <c r="M3" t="n">
-        <v>6.270062252810644</v>
+        <v>6.259049913514339</v>
       </c>
       <c r="N3" t="n">
-        <v>53.87974711999377</v>
+        <v>53.78174918960931</v>
       </c>
       <c r="O3" t="n">
-        <v>7.340282495925737</v>
+        <v>7.333604106413798</v>
       </c>
       <c r="P3" t="n">
-        <v>347.1814875184266</v>
+        <v>347.180377846763</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25424,28 +25477,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1011769580007514</v>
+        <v>0.1010652171497204</v>
       </c>
       <c r="J4" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K4" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0166934158524441</v>
+        <v>0.01672605207584033</v>
       </c>
       <c r="M4" t="n">
-        <v>4.580304117484356</v>
+        <v>4.572519014846483</v>
       </c>
       <c r="N4" t="n">
-        <v>31.7526867801383</v>
+        <v>31.6950060067943</v>
       </c>
       <c r="O4" t="n">
-        <v>5.634952242933235</v>
+        <v>5.629831792051545</v>
       </c>
       <c r="P4" t="n">
-        <v>344.9315141621941</v>
+        <v>344.9326724196998</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25502,28 +25555,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2906569006998923</v>
+        <v>0.2929794870408816</v>
       </c>
       <c r="J5" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K5" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L5" t="n">
-        <v>0.13155466311597</v>
+        <v>0.1336033772343036</v>
       </c>
       <c r="M5" t="n">
-        <v>4.530125686648597</v>
+        <v>4.531033466160472</v>
       </c>
       <c r="N5" t="n">
-        <v>29.36777380293188</v>
+        <v>29.38191286271058</v>
       </c>
       <c r="O5" t="n">
-        <v>5.419204166935573</v>
+        <v>5.420508542813172</v>
       </c>
       <c r="P5" t="n">
-        <v>334.4063533663137</v>
+        <v>334.3822784372508</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25580,28 +25633,28 @@
         <v>0.144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3832256600890775</v>
+        <v>0.3827745739140501</v>
       </c>
       <c r="J6" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K6" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2017336702424276</v>
+        <v>0.2029782807703888</v>
       </c>
       <c r="M6" t="n">
-        <v>4.591312051242306</v>
+        <v>4.581244926964158</v>
       </c>
       <c r="N6" t="n">
-        <v>30.60216077495323</v>
+        <v>30.36778203190579</v>
       </c>
       <c r="O6" t="n">
-        <v>5.531921978386285</v>
+        <v>5.510697054992752</v>
       </c>
       <c r="P6" t="n">
-        <v>322.3599939325452</v>
+        <v>322.3646208632466</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25658,28 +25711,28 @@
         <v>0.1548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3498937319775301</v>
+        <v>0.3485770173654279</v>
       </c>
       <c r="J7" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K7" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1861787221221969</v>
+        <v>0.1865277847980327</v>
       </c>
       <c r="M7" t="n">
-        <v>4.331863230991392</v>
+        <v>4.317582217727248</v>
       </c>
       <c r="N7" t="n">
-        <v>28.22051759253354</v>
+        <v>28.01011256060839</v>
       </c>
       <c r="O7" t="n">
-        <v>5.312298710777995</v>
+        <v>5.292458083027998</v>
       </c>
       <c r="P7" t="n">
-        <v>317.4121681926034</v>
+        <v>317.4257850952226</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25736,28 +25789,28 @@
         <v>0.0581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03815212786878205</v>
+        <v>0.03977414187576754</v>
       </c>
       <c r="J8" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K8" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002785593622993354</v>
+        <v>0.003035811360745377</v>
       </c>
       <c r="M8" t="n">
-        <v>4.181637388311281</v>
+        <v>4.183543781082867</v>
       </c>
       <c r="N8" t="n">
-        <v>27.43985571696834</v>
+        <v>27.42285941932986</v>
       </c>
       <c r="O8" t="n">
-        <v>5.238306569586047</v>
+        <v>5.236684009879712</v>
       </c>
       <c r="P8" t="n">
-        <v>311.6925102984777</v>
+        <v>311.6756972003086</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25795,7 +25848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I549"/>
+  <dimension ref="A1:I550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51570,12 +51623,12 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>-36.95601116464466,175.8425248954508</t>
+          <t>-36.95604411987599,175.8424613636469</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>-36.95666935090727,175.84297198340832</t>
+          <t>-36.956708335936476,175.8429162075117</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -51584,6 +51637,53 @@
         </is>
       </c>
       <c r="I549" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-36.95324006910626,175.84160614061204</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-36.95396346767232,175.8416359857877</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-36.954681028481595,175.84177183484823</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-36.95536567367396,175.84210410351693</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-36.956047151364494,175.84245551947217</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-36.956713600984095,175.84290867479896</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-36.95731702676253,175.84348093795987</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0185/nzd0185.xlsx
+++ b/data/nzd0185/nzd0185.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I550"/>
+  <dimension ref="A1:I553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18584,6 +18584,105 @@
         <v>316.96</v>
       </c>
       <c r="I550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>352.31</v>
+      </c>
+      <c r="C551" t="n">
+        <v>352.88</v>
+      </c>
+      <c r="D551" t="n">
+        <v>347.55</v>
+      </c>
+      <c r="E551" t="n">
+        <v>347.94</v>
+      </c>
+      <c r="F551" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="G551" t="n">
+        <v>329.27</v>
+      </c>
+      <c r="H551" t="n">
+        <v>317.69</v>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="C552" t="n">
+        <v>354.94</v>
+      </c>
+      <c r="D552" t="n">
+        <v>348.62</v>
+      </c>
+      <c r="E552" t="n">
+        <v>348.04</v>
+      </c>
+      <c r="F552" t="n">
+        <v>338.92</v>
+      </c>
+      <c r="G552" t="n">
+        <v>328.66</v>
+      </c>
+      <c r="H552" t="n">
+        <v>315.63</v>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="C553" t="n">
+        <v>355.74</v>
+      </c>
+      <c r="D553" t="n">
+        <v>348.94</v>
+      </c>
+      <c r="E553" t="n">
+        <v>347.54</v>
+      </c>
+      <c r="F553" t="n">
+        <v>338.52</v>
+      </c>
+      <c r="G553" t="n">
+        <v>327.66</v>
+      </c>
+      <c r="H553" t="n">
+        <v>315.79</v>
+      </c>
+      <c r="I553" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18600,7 +18699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B655"/>
+  <dimension ref="A1:B659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25153,6 +25252,46 @@
       </c>
       <c r="B655" t="n">
         <v>-0.41</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -25321,28 +25460,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2057847854639174</v>
+        <v>-0.2056408317593112</v>
       </c>
       <c r="J2" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="K2" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05863853860149359</v>
+        <v>0.05924617416673117</v>
       </c>
       <c r="M2" t="n">
-        <v>4.818575694191575</v>
+        <v>4.796697095670353</v>
       </c>
       <c r="N2" t="n">
-        <v>35.88443599849348</v>
+        <v>35.6949466167055</v>
       </c>
       <c r="O2" t="n">
-        <v>5.990361925501119</v>
+        <v>5.974524802585181</v>
       </c>
       <c r="P2" t="n">
-        <v>358.7214176207977</v>
+        <v>358.7199190703006</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25399,28 +25538,28 @@
         <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1757218128160311</v>
+        <v>0.1787977874119679</v>
       </c>
       <c r="J3" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="K3" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02941417649984945</v>
+        <v>0.03076592015984492</v>
       </c>
       <c r="M3" t="n">
-        <v>6.259049913514339</v>
+        <v>6.236708561096125</v>
       </c>
       <c r="N3" t="n">
-        <v>53.78174918960931</v>
+        <v>53.53716857387015</v>
       </c>
       <c r="O3" t="n">
-        <v>7.333604106413798</v>
+        <v>7.316909769422482</v>
       </c>
       <c r="P3" t="n">
-        <v>347.180377846763</v>
+        <v>347.1484231738098</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25477,28 +25616,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1010652171497204</v>
+        <v>0.101952577699556</v>
       </c>
       <c r="J4" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="K4" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01672605207584033</v>
+        <v>0.01722373896064833</v>
       </c>
       <c r="M4" t="n">
-        <v>4.572519014846483</v>
+        <v>4.551849637422076</v>
       </c>
       <c r="N4" t="n">
-        <v>31.6950060067943</v>
+        <v>31.52796901462647</v>
       </c>
       <c r="O4" t="n">
-        <v>5.629831792051545</v>
+        <v>5.614977205174253</v>
       </c>
       <c r="P4" t="n">
-        <v>344.9326724196998</v>
+        <v>344.9234519644492</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25555,28 +25694,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2929794870408816</v>
+        <v>0.2994742354223037</v>
       </c>
       <c r="J5" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="K5" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1336033772343036</v>
+        <v>0.1395307382781238</v>
       </c>
       <c r="M5" t="n">
-        <v>4.531033466160472</v>
+        <v>4.531854711110586</v>
       </c>
       <c r="N5" t="n">
-        <v>29.38191286271058</v>
+        <v>29.40063762020208</v>
       </c>
       <c r="O5" t="n">
-        <v>5.420508542813172</v>
+        <v>5.422235481810254</v>
       </c>
       <c r="P5" t="n">
-        <v>334.3822784372508</v>
+        <v>334.3148323940176</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25633,28 +25772,28 @@
         <v>0.144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3827745739140501</v>
+        <v>0.3897841606849256</v>
       </c>
       <c r="J6" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="K6" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2029782807703888</v>
+        <v>0.2098493747986919</v>
       </c>
       <c r="M6" t="n">
-        <v>4.581244926964158</v>
+        <v>4.581895352640402</v>
       </c>
       <c r="N6" t="n">
-        <v>30.36778203190579</v>
+        <v>30.41045608371909</v>
       </c>
       <c r="O6" t="n">
-        <v>5.510697054992752</v>
+        <v>5.514567624367217</v>
       </c>
       <c r="P6" t="n">
-        <v>322.3646208632466</v>
+        <v>322.2918264978373</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25711,28 +25850,28 @@
         <v>0.1548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3485770173654279</v>
+        <v>0.3507874471828649</v>
       </c>
       <c r="J7" t="n">
+        <v>552</v>
+      </c>
+      <c r="K7" t="n">
         <v>549</v>
       </c>
-      <c r="K7" t="n">
-        <v>546</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1865277847980327</v>
+        <v>0.1902420517270349</v>
       </c>
       <c r="M7" t="n">
-        <v>4.317582217727248</v>
+        <v>4.304481933440647</v>
       </c>
       <c r="N7" t="n">
-        <v>28.01011256060839</v>
+        <v>27.88022443913148</v>
       </c>
       <c r="O7" t="n">
-        <v>5.292458083027998</v>
+        <v>5.280172766030622</v>
       </c>
       <c r="P7" t="n">
-        <v>317.4257850952226</v>
+        <v>317.4028080919418</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25789,28 +25928,28 @@
         <v>0.0581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03977414187576754</v>
+        <v>0.04387738999688606</v>
       </c>
       <c r="J8" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="K8" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003035811360745377</v>
+        <v>0.003728026733638923</v>
       </c>
       <c r="M8" t="n">
-        <v>4.183543781082867</v>
+        <v>4.184693324167736</v>
       </c>
       <c r="N8" t="n">
-        <v>27.42285941932986</v>
+        <v>27.34971582670169</v>
       </c>
       <c r="O8" t="n">
-        <v>5.236684009879712</v>
+        <v>5.229695576866945</v>
       </c>
       <c r="P8" t="n">
-        <v>311.6756972003086</v>
+        <v>311.6330922801982</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25848,7 +25987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I550"/>
+  <dimension ref="A1:I553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51689,6 +51828,147 @@
         </is>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-36.95324117573078,175.8415880113113</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-36.95396234842521,175.8416450826585</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-36.954680325640936,175.84177461843382</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-36.95536638901655,175.8421022905428</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-36.95604451103581,175.84246060955982</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-36.95671596729749,175.84290528930975</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-36.95731221684094,175.8434865245238</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-36.95323951579296,175.84161520526214</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-36.95395953665505,175.8416679357715</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-36.95467743318066,175.84178607395853</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-36.955365991604005,175.84210329775067</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-36.956042261866756,175.84246494556015</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-36.95671957592525,175.84290012643828</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>-36.95732579004374,175.8434707596978</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-36.95324049262955,175.84159920223777</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-36.9539584447043,175.8416768107663</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-36.95467656814561,175.84178949990965</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-36.9553679786666,175.84209826171133</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-36.956044217665934,175.84246117512512</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-36.95672549170803,175.84289166271353</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>-36.95732473581447,175.8434719841505</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0185/nzd0185.xlsx
+++ b/data/nzd0185/nzd0185.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I553"/>
+  <dimension ref="A1:I554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18685,6 +18685,39 @@
       <c r="I553" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>354.55</v>
+      </c>
+      <c r="C554" t="n">
+        <v>356.01</v>
+      </c>
+      <c r="D554" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="E554" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="F554" t="n">
+        <v>338.69</v>
+      </c>
+      <c r="G554" t="n">
+        <v>327.93</v>
+      </c>
+      <c r="H554" t="n">
+        <v>316.23</v>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18699,7 +18732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B659"/>
+  <dimension ref="A1:B660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25292,6 +25325,16 @@
       </c>
       <c r="B659" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -25460,28 +25503,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2056408317593112</v>
+        <v>-0.2051788180838437</v>
       </c>
       <c r="J2" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K2" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05924617416673117</v>
+        <v>0.05922269568366434</v>
       </c>
       <c r="M2" t="n">
-        <v>4.796697095670353</v>
+        <v>4.789820291496349</v>
       </c>
       <c r="N2" t="n">
-        <v>35.6949466167055</v>
+        <v>35.63313122699488</v>
       </c>
       <c r="O2" t="n">
-        <v>5.974524802585181</v>
+        <v>5.969349313534506</v>
       </c>
       <c r="P2" t="n">
-        <v>358.7199190703006</v>
+        <v>358.7151079973502</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25538,28 +25581,28 @@
         <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1787977874119679</v>
+        <v>0.1803588275247593</v>
       </c>
       <c r="J3" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K3" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03076592015984492</v>
+        <v>0.03139699781431271</v>
       </c>
       <c r="M3" t="n">
-        <v>6.236708561096125</v>
+        <v>6.231360467548273</v>
       </c>
       <c r="N3" t="n">
-        <v>53.53716857387015</v>
+        <v>53.47155012636412</v>
       </c>
       <c r="O3" t="n">
-        <v>7.316909769422482</v>
+        <v>7.312424367223508</v>
       </c>
       <c r="P3" t="n">
-        <v>347.1484231738098</v>
+        <v>347.1321676422962</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25616,28 +25659,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.101952577699556</v>
+        <v>0.1025234180434147</v>
       </c>
       <c r="J4" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K4" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01722373896064833</v>
+        <v>0.01748272504636283</v>
       </c>
       <c r="M4" t="n">
-        <v>4.551849637422076</v>
+        <v>4.546229213675248</v>
       </c>
       <c r="N4" t="n">
-        <v>31.52796901462647</v>
+        <v>31.47512769266365</v>
       </c>
       <c r="O4" t="n">
-        <v>5.614977205174253</v>
+        <v>5.610269841341293</v>
       </c>
       <c r="P4" t="n">
-        <v>344.9234519644492</v>
+        <v>344.9175076500638</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25694,28 +25737,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2994742354223037</v>
+        <v>0.3015268949977588</v>
       </c>
       <c r="J5" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K5" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1395307382781238</v>
+        <v>0.1414603222491998</v>
       </c>
       <c r="M5" t="n">
-        <v>4.531854711110586</v>
+        <v>4.531644581275117</v>
       </c>
       <c r="N5" t="n">
-        <v>29.40063762020208</v>
+        <v>29.40140731076779</v>
       </c>
       <c r="O5" t="n">
-        <v>5.422235481810254</v>
+        <v>5.422306456736634</v>
       </c>
       <c r="P5" t="n">
-        <v>334.3148323940176</v>
+        <v>334.2934574965105</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25772,28 +25815,28 @@
         <v>0.144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3897841606849256</v>
+        <v>0.3920909964889886</v>
       </c>
       <c r="J6" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K6" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2098493747986919</v>
+        <v>0.2121323534754121</v>
       </c>
       <c r="M6" t="n">
-        <v>4.581895352640402</v>
+        <v>4.581945195296821</v>
       </c>
       <c r="N6" t="n">
-        <v>30.41045608371909</v>
+        <v>30.42358410871156</v>
       </c>
       <c r="O6" t="n">
-        <v>5.514567624367217</v>
+        <v>5.515757800040857</v>
       </c>
       <c r="P6" t="n">
-        <v>322.2918264978373</v>
+        <v>322.2678047947419</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25850,28 +25893,28 @@
         <v>0.1548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3507874471828649</v>
+        <v>0.351278716865329</v>
       </c>
       <c r="J7" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K7" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1902420517270349</v>
+        <v>0.1912968275111607</v>
       </c>
       <c r="M7" t="n">
-        <v>4.304481933440647</v>
+        <v>4.299009183985008</v>
       </c>
       <c r="N7" t="n">
-        <v>27.88022443913148</v>
+        <v>27.83263335359037</v>
       </c>
       <c r="O7" t="n">
-        <v>5.280172766030622</v>
+        <v>5.275664257095061</v>
       </c>
       <c r="P7" t="n">
-        <v>317.4028080919418</v>
+        <v>317.3976860190489</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25928,28 +25971,28 @@
         <v>0.0581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04387738999688606</v>
+        <v>0.04516789020515524</v>
       </c>
       <c r="J8" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K8" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003728026733638923</v>
+        <v>0.003962959288842938</v>
       </c>
       <c r="M8" t="n">
-        <v>4.184693324167736</v>
+        <v>4.1845853041179</v>
       </c>
       <c r="N8" t="n">
-        <v>27.34971582670169</v>
+        <v>27.32157731462479</v>
       </c>
       <c r="O8" t="n">
-        <v>5.229695576866945</v>
+        <v>5.227004621637978</v>
       </c>
       <c r="P8" t="n">
-        <v>311.6330922801982</v>
+        <v>311.6196539536416</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25987,7 +26030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I553"/>
+  <dimension ref="A1:I554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51969,6 +52012,53 @@
         </is>
       </c>
     </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-36.95323964558255,175.84161307898623</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-36.95395807617077,175.841679806077</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-36.95467605453101,175.8417915340681</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-36.95536750177159,175.8420994703608</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-36.956043386451285,175.84246277756003</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-36.956723894446725,175.84289394791935</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>-36.957321836683896,175.84347535139526</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0185/nzd0185.xlsx
+++ b/data/nzd0185/nzd0185.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I554"/>
+  <dimension ref="A1:I555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18718,6 +18718,39 @@
       <c r="I554" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:06:16+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="C555" t="n">
+        <v>355.83</v>
+      </c>
+      <c r="D555" t="n">
+        <v>348.43</v>
+      </c>
+      <c r="E555" t="n">
+        <v>347.68</v>
+      </c>
+      <c r="F555" t="n">
+        <v>339.27</v>
+      </c>
+      <c r="G555" t="n">
+        <v>327.31</v>
+      </c>
+      <c r="H555" t="n">
+        <v>316.33</v>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18732,7 +18765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B660"/>
+  <dimension ref="A1:B661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25335,6 +25368,16 @@
       </c>
       <c r="B660" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -25503,28 +25546,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2051788180838437</v>
+        <v>-0.2046193274733126</v>
       </c>
       <c r="J2" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K2" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05922269568366434</v>
+        <v>0.05914458891859975</v>
       </c>
       <c r="M2" t="n">
-        <v>4.789820291496349</v>
+        <v>4.783331747636225</v>
       </c>
       <c r="N2" t="n">
-        <v>35.63313122699488</v>
+        <v>35.57281161984481</v>
       </c>
       <c r="O2" t="n">
-        <v>5.969349313534506</v>
+        <v>5.964294729458363</v>
       </c>
       <c r="P2" t="n">
-        <v>358.7151079973502</v>
+        <v>358.7092658990767</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25581,28 +25624,28 @@
         <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1803588275247593</v>
+        <v>0.1818384109701586</v>
       </c>
       <c r="J3" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K3" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03139699781431271</v>
+        <v>0.03201055410756803</v>
       </c>
       <c r="M3" t="n">
-        <v>6.231360467548273</v>
+        <v>6.225681795893995</v>
       </c>
       <c r="N3" t="n">
-        <v>53.47155012636412</v>
+        <v>53.4030058711653</v>
       </c>
       <c r="O3" t="n">
-        <v>7.312424367223508</v>
+        <v>7.307736029110883</v>
       </c>
       <c r="P3" t="n">
-        <v>347.1321676422962</v>
+        <v>347.1167181035032</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25659,28 +25702,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1025234180434147</v>
+        <v>0.102828703216653</v>
       </c>
       <c r="J4" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K4" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01748272504636283</v>
+        <v>0.01765670618063475</v>
       </c>
       <c r="M4" t="n">
-        <v>4.546229213675248</v>
+        <v>4.539408687426962</v>
       </c>
       <c r="N4" t="n">
-        <v>31.47512769266365</v>
+        <v>31.41950434859582</v>
       </c>
       <c r="O4" t="n">
-        <v>5.610269841341293</v>
+        <v>5.605310370407317</v>
       </c>
       <c r="P4" t="n">
-        <v>344.9175076500638</v>
+        <v>344.914319918313</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25737,28 +25780,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3015268949977588</v>
+        <v>0.3035676998347285</v>
       </c>
       <c r="J5" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K5" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1414603222491998</v>
+        <v>0.1433962409212305</v>
       </c>
       <c r="M5" t="n">
-        <v>4.531644581275117</v>
+        <v>4.531432546128146</v>
       </c>
       <c r="N5" t="n">
-        <v>29.40140731076779</v>
+        <v>29.40155813453301</v>
       </c>
       <c r="O5" t="n">
-        <v>5.422306456736634</v>
+        <v>5.42232036443191</v>
       </c>
       <c r="P5" t="n">
-        <v>334.2934574965105</v>
+        <v>334.2721477869461</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25815,28 +25858,28 @@
         <v>0.144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3920909964889886</v>
+        <v>0.3945923685433123</v>
       </c>
       <c r="J6" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K6" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2121323534754121</v>
+        <v>0.2145254595896602</v>
       </c>
       <c r="M6" t="n">
-        <v>4.581945195296821</v>
+        <v>4.582633871877143</v>
       </c>
       <c r="N6" t="n">
-        <v>30.42358410871156</v>
+        <v>30.4486226787099</v>
       </c>
       <c r="O6" t="n">
-        <v>5.515757800040857</v>
+        <v>5.518027063970409</v>
       </c>
       <c r="P6" t="n">
-        <v>322.2678047947419</v>
+        <v>322.2416859268205</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25893,28 +25936,28 @@
         <v>0.1548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.351278716865329</v>
+        <v>0.3515253028976563</v>
       </c>
       <c r="J7" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K7" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1912968275111607</v>
+        <v>0.1921549362796822</v>
       </c>
       <c r="M7" t="n">
-        <v>4.299009183985008</v>
+        <v>4.292382512410647</v>
       </c>
       <c r="N7" t="n">
-        <v>27.83263335359037</v>
+        <v>27.78290009290084</v>
       </c>
       <c r="O7" t="n">
-        <v>5.275664257095061</v>
+        <v>5.270948690027332</v>
       </c>
       <c r="P7" t="n">
-        <v>317.3976860190489</v>
+        <v>317.3951079725052</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25971,28 +26014,28 @@
         <v>0.0581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04516789020515524</v>
+        <v>0.04648673160763743</v>
       </c>
       <c r="J8" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K8" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003962959288842938</v>
+        <v>0.004210828042702341</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1845853041179</v>
+        <v>4.184602865236927</v>
       </c>
       <c r="N8" t="n">
-        <v>27.32157731462479</v>
+        <v>27.2944869877431</v>
       </c>
       <c r="O8" t="n">
-        <v>5.227004621637978</v>
+        <v>5.224412597387682</v>
       </c>
       <c r="P8" t="n">
-        <v>311.6196539536416</v>
+        <v>311.6058828537601</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26030,7 +26073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I554"/>
+  <dimension ref="A1:I555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52059,6 +52102,53 @@
         </is>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:06:16+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-36.953239474806765,175.84161587671773</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-36.95395832185981,175.8416778092032</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-36.95467794679518,175.8417840398</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-36.9553674222891,175.8420996718024</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-36.95604055054238,175.84246824469068</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-36.956727562231855,175.84288870040956</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>-36.957321177790575,175.84347611667812</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0185/nzd0185.xlsx
+++ b/data/nzd0185/nzd0185.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I555"/>
+  <dimension ref="A1:I556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18751,6 +18751,39 @@
       <c r="I555" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>357.16</v>
+      </c>
+      <c r="C556" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="D556" t="n">
+        <v>348.86</v>
+      </c>
+      <c r="E556" t="n">
+        <v>349.27</v>
+      </c>
+      <c r="F556" t="n">
+        <v>338.82</v>
+      </c>
+      <c r="G556" t="n">
+        <v>325.78</v>
+      </c>
+      <c r="H556" t="n">
+        <v>313.8</v>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18765,7 +18798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B661"/>
+  <dimension ref="A1:B662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25378,6 +25411,16 @@
       </c>
       <c r="B661" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>-0.41</v>
       </c>
     </row>
   </sheetData>
@@ -25546,28 +25589,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2046193274733126</v>
+        <v>-0.2031763557014821</v>
       </c>
       <c r="J2" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K2" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05914458891859975</v>
+        <v>0.05855119726302416</v>
       </c>
       <c r="M2" t="n">
-        <v>4.783331747636225</v>
+        <v>4.780273922332495</v>
       </c>
       <c r="N2" t="n">
-        <v>35.57281161984481</v>
+        <v>35.53527999619489</v>
       </c>
       <c r="O2" t="n">
-        <v>5.964294729458363</v>
+        <v>5.96114754021362</v>
       </c>
       <c r="P2" t="n">
-        <v>358.7092658990767</v>
+        <v>358.6941577011658</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25624,28 +25667,28 @@
         <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1818384109701586</v>
+        <v>0.1842336127770212</v>
       </c>
       <c r="J3" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K3" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03201055410756803</v>
+        <v>0.03292105787307265</v>
       </c>
       <c r="M3" t="n">
-        <v>6.225681795893995</v>
+        <v>6.223662586532472</v>
       </c>
       <c r="N3" t="n">
-        <v>53.4030058711653</v>
+        <v>53.37997468228897</v>
       </c>
       <c r="O3" t="n">
-        <v>7.307736029110883</v>
+        <v>7.306160050415606</v>
       </c>
       <c r="P3" t="n">
-        <v>347.1167181035032</v>
+        <v>347.0916398700677</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25702,28 +25745,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.102828703216653</v>
+        <v>0.1032891037439637</v>
       </c>
       <c r="J4" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K4" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01765670618063475</v>
+        <v>0.01788424544474165</v>
       </c>
       <c r="M4" t="n">
-        <v>4.539408687426962</v>
+        <v>4.533303472780124</v>
       </c>
       <c r="N4" t="n">
-        <v>31.41950434859582</v>
+        <v>31.36559684755942</v>
       </c>
       <c r="O4" t="n">
-        <v>5.605310370407317</v>
+        <v>5.600499696237776</v>
       </c>
       <c r="P4" t="n">
-        <v>344.914319918313</v>
+        <v>344.9094994343502</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25780,28 +25823,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3035676998347285</v>
+        <v>0.3061826705677353</v>
       </c>
       <c r="J5" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K5" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1433962409212305</v>
+        <v>0.1456680209649925</v>
       </c>
       <c r="M5" t="n">
-        <v>4.531432546128146</v>
+        <v>4.533392604309718</v>
       </c>
       <c r="N5" t="n">
-        <v>29.40155813453301</v>
+        <v>29.43581997670449</v>
       </c>
       <c r="O5" t="n">
-        <v>5.42232036443191</v>
+        <v>5.425478778569177</v>
       </c>
       <c r="P5" t="n">
-        <v>334.2721477869461</v>
+        <v>334.2447685296821</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25858,28 +25901,28 @@
         <v>0.144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3945923685433123</v>
+        <v>0.3968983069333983</v>
       </c>
       <c r="J6" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K6" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2145254595896602</v>
+        <v>0.2168280362030963</v>
       </c>
       <c r="M6" t="n">
-        <v>4.582633871877143</v>
+        <v>4.582585185417391</v>
       </c>
       <c r="N6" t="n">
-        <v>30.4486226787099</v>
+        <v>30.46159712715997</v>
       </c>
       <c r="O6" t="n">
-        <v>5.518027063970409</v>
+        <v>5.519202580732109</v>
       </c>
       <c r="P6" t="n">
-        <v>322.2416859268205</v>
+        <v>322.2175422988938</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25936,28 +25979,28 @@
         <v>0.1548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3515253028976563</v>
+        <v>0.3511892542784597</v>
       </c>
       <c r="J7" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K7" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1921549362796822</v>
+        <v>0.1924988398117222</v>
       </c>
       <c r="M7" t="n">
-        <v>4.292382512410647</v>
+        <v>4.286243432051641</v>
       </c>
       <c r="N7" t="n">
-        <v>27.78290009290084</v>
+        <v>27.73401435716732</v>
       </c>
       <c r="O7" t="n">
-        <v>5.270948690027332</v>
+        <v>5.266309367779994</v>
       </c>
       <c r="P7" t="n">
-        <v>317.3951079725052</v>
+        <v>317.3986309558388</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26014,28 +26057,28 @@
         <v>0.0581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04648673160763743</v>
+        <v>0.04684777161259754</v>
       </c>
       <c r="J8" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K8" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004210828042702341</v>
+        <v>0.004293815087180519</v>
       </c>
       <c r="M8" t="n">
-        <v>4.184602865236927</v>
+        <v>4.179121486007546</v>
       </c>
       <c r="N8" t="n">
-        <v>27.2944869877431</v>
+        <v>27.24697068810479</v>
       </c>
       <c r="O8" t="n">
-        <v>5.224412597387682</v>
+        <v>5.219863090934933</v>
       </c>
       <c r="P8" t="n">
-        <v>311.6058828537601</v>
+        <v>311.6021026939848</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26073,7 +26116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I555"/>
+  <dimension ref="A1:I556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52149,6 +52192,53 @@
         </is>
       </c>
     </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-36.95323786268002,175.84164228730214</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-36.95395493680812,175.84170532168517</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-36.95467678440438,175.8417886434219</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-36.95536110342913,175.84211568640623</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-36.956042750816565,175.8424640029514</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-36.95673661337812,175.8428757509074</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-36.95733784779029,175.84345675501757</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0185/nzd0185.xlsx
+++ b/data/nzd0185/nzd0185.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I556"/>
+  <dimension ref="A1:I558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18782,6 +18782,72 @@
         <v>313.8</v>
       </c>
       <c r="I556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>356.74</v>
+      </c>
+      <c r="C557" t="n">
+        <v>357.81</v>
+      </c>
+      <c r="D557" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="E557" t="n">
+        <v>349.08</v>
+      </c>
+      <c r="F557" t="n">
+        <v>337.76</v>
+      </c>
+      <c r="G557" t="n">
+        <v>324.16</v>
+      </c>
+      <c r="H557" t="n">
+        <v>311.91</v>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>357.59</v>
+      </c>
+      <c r="C558" t="n">
+        <v>357.67</v>
+      </c>
+      <c r="D558" t="n">
+        <v>349.34</v>
+      </c>
+      <c r="E558" t="n">
+        <v>348.85</v>
+      </c>
+      <c r="F558" t="n">
+        <v>337.88</v>
+      </c>
+      <c r="G558" t="n">
+        <v>326.38</v>
+      </c>
+      <c r="H558" t="n">
+        <v>312.57</v>
+      </c>
+      <c r="I558" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18798,7 +18864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B662"/>
+  <dimension ref="A1:B665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25421,6 +25487,36 @@
       </c>
       <c r="B662" t="n">
         <v>-0.41</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -25589,28 +25685,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2031763557014821</v>
+        <v>-0.2003073193123364</v>
       </c>
       <c r="J2" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K2" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05855119726302416</v>
+        <v>0.05737343154877883</v>
       </c>
       <c r="M2" t="n">
-        <v>4.780273922332495</v>
+        <v>4.774221372348171</v>
       </c>
       <c r="N2" t="n">
-        <v>35.53527999619489</v>
+        <v>35.46095654574774</v>
       </c>
       <c r="O2" t="n">
-        <v>5.96114754021362</v>
+        <v>5.954910288639766</v>
       </c>
       <c r="P2" t="n">
-        <v>358.6941577011658</v>
+        <v>358.6640343718758</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25667,28 +25763,28 @@
         <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1842336127770212</v>
+        <v>0.1885295737633025</v>
       </c>
       <c r="J3" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K3" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03292105787307265</v>
+        <v>0.03462609038209274</v>
       </c>
       <c r="M3" t="n">
-        <v>6.223662586532472</v>
+        <v>6.217645954342367</v>
       </c>
       <c r="N3" t="n">
-        <v>53.37997468228897</v>
+        <v>53.30636008368382</v>
       </c>
       <c r="O3" t="n">
-        <v>7.306160050415606</v>
+        <v>7.301120467687396</v>
       </c>
       <c r="P3" t="n">
-        <v>347.0916398700677</v>
+        <v>347.0465396258229</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25745,28 +25841,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1032891037439637</v>
+        <v>0.1043386733251368</v>
       </c>
       <c r="J4" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K4" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01788424544474165</v>
+        <v>0.01838927666630286</v>
       </c>
       <c r="M4" t="n">
-        <v>4.533303472780124</v>
+        <v>4.52170769853809</v>
       </c>
       <c r="N4" t="n">
-        <v>31.36559684755942</v>
+        <v>31.26030609522318</v>
       </c>
       <c r="O4" t="n">
-        <v>5.600499696237776</v>
+        <v>5.591091672940373</v>
       </c>
       <c r="P4" t="n">
-        <v>344.9094994343502</v>
+        <v>344.8984786068364</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25823,28 +25919,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3061826705677353</v>
+        <v>0.311106835255316</v>
       </c>
       <c r="J5" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K5" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1456680209649925</v>
+        <v>0.1500792097775366</v>
       </c>
       <c r="M5" t="n">
-        <v>4.533392604309718</v>
+        <v>4.536056179417315</v>
       </c>
       <c r="N5" t="n">
-        <v>29.43581997670449</v>
+        <v>29.48526142938918</v>
       </c>
       <c r="O5" t="n">
-        <v>5.425478778569177</v>
+        <v>5.430033280688911</v>
       </c>
       <c r="P5" t="n">
-        <v>334.2447685296821</v>
+        <v>334.1930734708758</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25901,28 +25997,28 @@
         <v>0.144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3968983069333983</v>
+        <v>0.4006922883928845</v>
       </c>
       <c r="J6" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K6" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2168280362030963</v>
+        <v>0.2209957902253513</v>
       </c>
       <c r="M6" t="n">
-        <v>4.582585185417391</v>
+        <v>4.579628278395505</v>
       </c>
       <c r="N6" t="n">
-        <v>30.46159712715997</v>
+        <v>30.44428160917932</v>
       </c>
       <c r="O6" t="n">
-        <v>5.519202580732109</v>
+        <v>5.5176336965387</v>
       </c>
       <c r="P6" t="n">
-        <v>322.2175422988938</v>
+        <v>322.1777111902252</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25979,28 +26075,28 @@
         <v>0.1548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3511892542784597</v>
+        <v>0.350128025175037</v>
       </c>
       <c r="J7" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K7" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1924988398117222</v>
+        <v>0.19279197319077</v>
       </c>
       <c r="M7" t="n">
-        <v>4.286243432051641</v>
+        <v>4.275959223702971</v>
       </c>
       <c r="N7" t="n">
-        <v>27.73401435716732</v>
+        <v>27.64553432202122</v>
       </c>
       <c r="O7" t="n">
-        <v>5.266309367779994</v>
+        <v>5.257902083723242</v>
       </c>
       <c r="P7" t="n">
-        <v>317.3986309558388</v>
+        <v>317.4097787335954</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26057,28 +26153,28 @@
         <v>0.0581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04684777161259754</v>
+        <v>0.04640040959818251</v>
       </c>
       <c r="J8" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K8" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004293815087180519</v>
+        <v>0.004247566325206953</v>
       </c>
       <c r="M8" t="n">
-        <v>4.179121486007546</v>
+        <v>4.165851253084306</v>
       </c>
       <c r="N8" t="n">
-        <v>27.24697068810479</v>
+        <v>27.15081023625929</v>
       </c>
       <c r="O8" t="n">
-        <v>5.219863090934933</v>
+        <v>5.210643936814267</v>
       </c>
       <c r="P8" t="n">
-        <v>311.6021026939848</v>
+        <v>311.6067969573205</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26116,7 +26212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I556"/>
+  <dimension ref="A1:I558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52239,6 +52335,100 @@
         </is>
       </c>
     </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-36.95323814958436,175.8416375871135</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-36.95395561927872,175.84169977481403</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-36.954677054727846,175.84178757281217</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-36.95536185851313,175.84211377271157</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-36.95604793368408,175.84245401129797</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-36.956746196943335,175.84286203966644</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-36.957350300871234,175.84344229116292</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-36.95323756894443,175.8416470994</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-36.95395581037044,175.84169822169008</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-36.95467548685165,175.84179378234845</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-36.95536277256215,175.84211145613378</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>-36.956047346944395,175.84245514242863</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-36.95673306390914,175.8428808291439</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-36.95734595217648,175.84344734203333</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0185/nzd0185.xlsx
+++ b/data/nzd0185/nzd0185.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I558"/>
+  <dimension ref="A1:I559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18848,6 +18848,39 @@
         <v>312.57</v>
       </c>
       <c r="I558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>358.33</v>
+      </c>
+      <c r="C559" t="n">
+        <v>357.56</v>
+      </c>
+      <c r="D559" t="n">
+        <v>349.29</v>
+      </c>
+      <c r="E559" t="n">
+        <v>348.93</v>
+      </c>
+      <c r="F559" t="n">
+        <v>337.57</v>
+      </c>
+      <c r="G559" t="n">
+        <v>326.52</v>
+      </c>
+      <c r="H559" t="n">
+        <v>313.46</v>
+      </c>
+      <c r="I559" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18864,7 +18897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B665"/>
+  <dimension ref="A1:B667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25517,6 +25550,26 @@
       </c>
       <c r="B665" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -25685,28 +25738,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2003073193123364</v>
+        <v>-0.1984453629072198</v>
       </c>
       <c r="J2" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K2" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05737343154877883</v>
+        <v>0.0565289840014116</v>
       </c>
       <c r="M2" t="n">
-        <v>4.774221372348171</v>
+        <v>4.772832293300264</v>
       </c>
       <c r="N2" t="n">
-        <v>35.46095654574774</v>
+        <v>35.44175297295283</v>
       </c>
       <c r="O2" t="n">
-        <v>5.954910288639766</v>
+        <v>5.953297655329592</v>
       </c>
       <c r="P2" t="n">
-        <v>358.6640343718758</v>
+        <v>358.6444146911623</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25763,28 +25816,28 @@
         <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1885295737633025</v>
+        <v>0.1905847144646529</v>
       </c>
       <c r="J3" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K3" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03462609038209274</v>
+        <v>0.03546730868124914</v>
       </c>
       <c r="M3" t="n">
-        <v>6.217645954342367</v>
+        <v>6.214223990738752</v>
       </c>
       <c r="N3" t="n">
-        <v>53.30636008368382</v>
+        <v>53.26485508668297</v>
       </c>
       <c r="O3" t="n">
-        <v>7.301120467687396</v>
+        <v>7.298277542453628</v>
       </c>
       <c r="P3" t="n">
-        <v>347.0465396258229</v>
+        <v>347.0248843366491</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25841,28 +25894,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1043386733251368</v>
+        <v>0.1049433289288548</v>
       </c>
       <c r="J4" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K4" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01838927666630286</v>
+        <v>0.01867324970929085</v>
       </c>
       <c r="M4" t="n">
-        <v>4.52170769853809</v>
+        <v>4.516276204800973</v>
       </c>
       <c r="N4" t="n">
-        <v>31.26030609522318</v>
+        <v>31.20896071183098</v>
       </c>
       <c r="O4" t="n">
-        <v>5.591091672940373</v>
+        <v>5.586498072301732</v>
       </c>
       <c r="P4" t="n">
-        <v>344.8984786068364</v>
+        <v>344.8921072708298</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25919,28 +25972,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.311106835255316</v>
+        <v>0.3135227033929724</v>
       </c>
       <c r="J5" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K5" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1500792097775366</v>
+        <v>0.1522791869796816</v>
       </c>
       <c r="M5" t="n">
-        <v>4.536056179417315</v>
+        <v>4.537134374657219</v>
       </c>
       <c r="N5" t="n">
-        <v>29.48526142938918</v>
+        <v>29.50707686252836</v>
       </c>
       <c r="O5" t="n">
-        <v>5.430033280688911</v>
+        <v>5.432041684535232</v>
       </c>
       <c r="P5" t="n">
-        <v>334.1930734708758</v>
+        <v>334.1676171490326</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25997,28 +26050,28 @@
         <v>0.144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4006922883928845</v>
+        <v>0.4024652049401868</v>
       </c>
       <c r="J6" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K6" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2209957902253513</v>
+        <v>0.2230190726023145</v>
       </c>
       <c r="M6" t="n">
-        <v>4.579628278395505</v>
+        <v>4.577691768667549</v>
       </c>
       <c r="N6" t="n">
-        <v>30.44428160917932</v>
+        <v>30.42992855079437</v>
       </c>
       <c r="O6" t="n">
-        <v>5.5176336965387</v>
+        <v>5.516332889773275</v>
       </c>
       <c r="P6" t="n">
-        <v>322.1777111902252</v>
+        <v>322.1590297342608</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26075,28 +26128,28 @@
         <v>0.1548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.350128025175037</v>
+        <v>0.3500550476308298</v>
       </c>
       <c r="J7" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K7" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L7" t="n">
-        <v>0.19279197319077</v>
+        <v>0.1933807147157681</v>
       </c>
       <c r="M7" t="n">
-        <v>4.275959223702971</v>
+        <v>4.268610342674991</v>
       </c>
       <c r="N7" t="n">
-        <v>27.64553432202122</v>
+        <v>27.59579089662644</v>
       </c>
       <c r="O7" t="n">
-        <v>5.257902083723242</v>
+        <v>5.253169604783995</v>
       </c>
       <c r="P7" t="n">
-        <v>317.4097787335954</v>
+        <v>317.4105487189894</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26153,28 +26206,28 @@
         <v>0.0581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04640040959818251</v>
+        <v>0.04663366550707698</v>
       </c>
       <c r="J8" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K8" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004247566325206953</v>
+        <v>0.004308092722720702</v>
       </c>
       <c r="M8" t="n">
-        <v>4.165851253084306</v>
+        <v>4.159719186084623</v>
       </c>
       <c r="N8" t="n">
-        <v>27.15081023625929</v>
+        <v>27.10284883287412</v>
       </c>
       <c r="O8" t="n">
-        <v>5.210643936814267</v>
+        <v>5.206039649568002</v>
       </c>
       <c r="P8" t="n">
-        <v>311.6067969573205</v>
+        <v>311.6043391089818</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26212,7 +26265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I558"/>
+  <dimension ref="A1:I559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52429,6 +52482,53 @@
         </is>
       </c>
     </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-36.95323706344552,175.84165538068453</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-36.95395596051393,175.84169700137844</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-36.9546756220134,175.84179324704363</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-36.95536245463206,175.84211226189998</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>-36.95604886268856,175.8424522203411</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>-36.956732235699704,175.84288201406568</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-36.957340088027195,175.84345415305467</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0185/nzd0185.xlsx
+++ b/data/nzd0185/nzd0185.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I559"/>
+  <dimension ref="A1:I562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18883,6 +18883,105 @@
       <c r="I559" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>363.66</v>
+      </c>
+      <c r="C560" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="D560" t="n">
+        <v>349.29</v>
+      </c>
+      <c r="E560" t="n">
+        <v>347.06</v>
+      </c>
+      <c r="F560" t="n">
+        <v>336.31</v>
+      </c>
+      <c r="G560" t="n">
+        <v>326.93</v>
+      </c>
+      <c r="H560" t="n">
+        <v>314.97</v>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="C561" t="n">
+        <v>357.25</v>
+      </c>
+      <c r="D561" t="n">
+        <v>350.08</v>
+      </c>
+      <c r="E561" t="n">
+        <v>347.01</v>
+      </c>
+      <c r="F561" t="n">
+        <v>335.47</v>
+      </c>
+      <c r="G561" t="n">
+        <v>327.65</v>
+      </c>
+      <c r="H561" t="n">
+        <v>318.18</v>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>362.42</v>
+      </c>
+      <c r="C562" t="n">
+        <v>354</v>
+      </c>
+      <c r="D562" t="n">
+        <v>349.16</v>
+      </c>
+      <c r="E562" t="n">
+        <v>345.66</v>
+      </c>
+      <c r="F562" t="n">
+        <v>333.77</v>
+      </c>
+      <c r="G562" t="n">
+        <v>327.59</v>
+      </c>
+      <c r="H562" t="n">
+        <v>317.03</v>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18897,7 +18996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B667"/>
+  <dimension ref="A1:B671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25570,6 +25669,46 @@
       </c>
       <c r="B667" t="n">
         <v>0.21</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -25738,28 +25877,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1984453629072198</v>
+        <v>-0.187915000174664</v>
       </c>
       <c r="J2" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K2" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0565289840014116</v>
+        <v>0.05096176135754704</v>
       </c>
       <c r="M2" t="n">
-        <v>4.772832293300264</v>
+        <v>4.787251542054353</v>
       </c>
       <c r="N2" t="n">
-        <v>35.44175297295283</v>
+        <v>35.72331583227976</v>
       </c>
       <c r="O2" t="n">
-        <v>5.953297655329592</v>
+        <v>5.976898512797399</v>
       </c>
       <c r="P2" t="n">
-        <v>358.6444146911623</v>
+        <v>358.5327861311866</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25816,28 +25955,28 @@
         <v>0.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1905847144646529</v>
+        <v>0.1951003998129404</v>
       </c>
       <c r="J3" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K3" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03546730868124914</v>
+        <v>0.03749606528796412</v>
       </c>
       <c r="M3" t="n">
-        <v>6.214223990738752</v>
+        <v>6.197683044426312</v>
       </c>
       <c r="N3" t="n">
-        <v>53.26485508668297</v>
+        <v>53.07899849059567</v>
       </c>
       <c r="O3" t="n">
-        <v>7.298277542453628</v>
+        <v>7.285533507616012</v>
       </c>
       <c r="P3" t="n">
-        <v>347.0248843366491</v>
+        <v>346.9770240954372</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25894,28 +26033,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1049433289288548</v>
+        <v>0.1069672914163499</v>
       </c>
       <c r="J4" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K4" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01867324970929085</v>
+        <v>0.01961918713034549</v>
       </c>
       <c r="M4" t="n">
-        <v>4.516276204800973</v>
+        <v>4.50092661974508</v>
       </c>
       <c r="N4" t="n">
-        <v>31.20896071183098</v>
+        <v>31.06028064985192</v>
       </c>
       <c r="O4" t="n">
-        <v>5.586498072301732</v>
+        <v>5.573175095926192</v>
       </c>
       <c r="P4" t="n">
-        <v>344.8921072708298</v>
+        <v>344.8706513254558</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25972,28 +26111,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3135227033929724</v>
+        <v>0.3180159431385622</v>
       </c>
       <c r="J5" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K5" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1522791869796816</v>
+        <v>0.1572811068885352</v>
       </c>
       <c r="M5" t="n">
-        <v>4.537134374657219</v>
+        <v>4.529655813897467</v>
       </c>
       <c r="N5" t="n">
-        <v>29.50707686252836</v>
+        <v>29.43699974313706</v>
       </c>
       <c r="O5" t="n">
-        <v>5.432041684535232</v>
+        <v>5.425587502117818</v>
       </c>
       <c r="P5" t="n">
-        <v>334.1676171490326</v>
+        <v>334.1199887244014</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26050,28 +26189,28 @@
         <v>0.144</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4024652049401868</v>
+        <v>0.4049946862796274</v>
       </c>
       <c r="J6" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K6" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2230190726023145</v>
+        <v>0.2272402827420594</v>
       </c>
       <c r="M6" t="n">
-        <v>4.577691768667549</v>
+        <v>4.562061032696852</v>
       </c>
       <c r="N6" t="n">
-        <v>30.42992855079437</v>
+        <v>30.30033209140692</v>
       </c>
       <c r="O6" t="n">
-        <v>5.516332889773275</v>
+        <v>5.504573742934771</v>
       </c>
       <c r="P6" t="n">
-        <v>322.1590297342608</v>
+        <v>322.1322232385272</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26128,28 +26267,28 @@
         <v>0.1548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3500550476308298</v>
+        <v>0.3507527266344657</v>
       </c>
       <c r="J7" t="n">
+        <v>561</v>
+      </c>
+      <c r="K7" t="n">
         <v>558</v>
       </c>
-      <c r="K7" t="n">
-        <v>555</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1933807147157681</v>
+        <v>0.1959868882610221</v>
       </c>
       <c r="M7" t="n">
-        <v>4.268610342674991</v>
+        <v>4.248934926688795</v>
       </c>
       <c r="N7" t="n">
-        <v>27.59579089662644</v>
+        <v>27.45004750285127</v>
       </c>
       <c r="O7" t="n">
-        <v>5.253169604783995</v>
+        <v>5.239279292312185</v>
       </c>
       <c r="P7" t="n">
-        <v>317.4105487189894</v>
+        <v>317.4031402145378</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26206,28 +26345,28 @@
         <v>0.0581</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04663366550707698</v>
+        <v>0.05095492291161864</v>
       </c>
       <c r="J8" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K8" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004308092722720702</v>
+        <v>0.005187951673201519</v>
       </c>
       <c r="M8" t="n">
-        <v>4.159719186084623</v>
+        <v>4.161761398676282</v>
       </c>
       <c r="N8" t="n">
-        <v>27.10284883287412</v>
+        <v>27.04624616953268</v>
       </c>
       <c r="O8" t="n">
-        <v>5.206039649568002</v>
+        <v>5.200600558544433</v>
       </c>
       <c r="P8" t="n">
-        <v>311.6043391089818</v>
+        <v>311.5585214746312</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26265,7 +26404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I559"/>
+  <dimension ref="A1:I562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52529,6 +52668,147 @@
         </is>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-36.953233422470255,175.84171502831086</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-36.953956369996085,175.84169367325563</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-36.9546756220134,175.84179324704363</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-36.95536988624651,175.84209342711333</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-36.9560550234544,175.84244034346793</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-36.95672981022909,175.8428854841936</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-36.957330138739394,175.84346570883002</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-36.95323435150242,175.84169980865457</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-36.9539563836455,175.84169356231823</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-36.95467348645744,175.8418017048599</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-36.95537008495273,175.84209292350937</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-36.956059130631026,175.8424324255514</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-36.95672555086584,175.8428915780763</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-36.9573089882633,175.84349027440877</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-36.953234269529084,175.84170115156545</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-36.953960819696334,175.84165750765223</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-36.95467597343394,175.84179185525102</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-36.95537545002016,175.84207932620106</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-36.956067442772664,175.84241640119384</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-36.95672590581279,175.84289107025273</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-36.95731656553719,175.84348147365782</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
